--- a/stats_unique_authors.xlsx
+++ b/stats_unique_authors.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,230 +512,302 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Cerner Corporation</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9119496855345912</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08163088267187169</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Clinical Practice Research Datalink</t>
+          <t>Cerner Corporation</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C3" t="n">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7717391304347826</v>
+        <v>0.9119496855345912</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2014696876913655</v>
+        <v>0.08163088267187169</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Flatiron Health</t>
+          <t>Clinical Practice Research Datalink</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>476</v>
+        <v>240</v>
       </c>
       <c r="C4" t="n">
-        <v>628</v>
+        <v>327</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7579617834394905</v>
+        <v>0.7339449541284404</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2022761333832896</v>
+        <v>0.2318425076452599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Flatiron Health</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76</v>
+        <v>539</v>
       </c>
       <c r="C5" t="n">
-        <v>82</v>
+        <v>720</v>
       </c>
       <c r="D5" t="n">
-        <v>0.926829268292683</v>
+        <v>0.7486111111111111</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06739409499358162</v>
+        <v>0.2103432282003712</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NPS MedicineWise</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9459459459459459</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05096525096525117</v>
+        <v>0.06739409499358162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>InGef</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>611</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>771</v>
+        <v>83</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7924773022049286</v>
+        <v>0.927710843373494</v>
       </c>
       <c r="E7" t="n">
-        <v>0.179502038927488</v>
+        <v>0.06915975590674406</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SAIL Databank</t>
+          <t>NPS MedicineWise</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>220</v>
+        <v>42</v>
       </c>
       <c r="C8" t="n">
-        <v>320</v>
+        <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6875</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2805397727272727</v>
+        <v>0.04329004329004338</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>South London and Maudsley NHS Foundation Trust</t>
+          <t>New York University Langone Health</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6217948717948718</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3231562252180809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>680</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>870</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.7816091954022989</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07867494824016563</v>
+        <v>0.1875185936443542</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>University of Minnesota</t>
+          <t>SAIL Databank</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>315</v>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>450</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2669172932330828</v>
+        <v>0.2717460317460318</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center</t>
+          <t>South London and Maudsley NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="C12" t="n">
-        <v>346</v>
+        <v>177</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6705202312138728</v>
+        <v>0.5932203389830508</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2778552920071755</v>
+        <v>0.3452246435297284</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>The Health Improvement Network</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>42</v>
+      </c>
+      <c r="C13" t="n">
+        <v>42</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TriNetX</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>85</v>
+      </c>
+      <c r="C14" t="n">
+        <v>105</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1570868347338936</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>University of Minnesota</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>19</v>
+      </c>
+      <c r="C15" t="n">
+        <v>28</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2669172932330828</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vanderbilt University Medical Center</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>277</v>
+      </c>
+      <c r="C16" t="n">
+        <v>412</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6723300970873787</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2744383302372857</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Western Australian Data Linkage System</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B17" t="n">
         <v>29</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C17" t="n">
         <v>31</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D17" t="n">
         <v>0.9354838709677419</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E17" t="n">
         <v>0.06006674082313679</v>
       </c>
     </row>

--- a/stats_unique_authors.xlsx
+++ b/stats_unique_authors.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,94 +512,98 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cerner Corporation</t>
+        </is>
+      </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>166</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.8177339901477833</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.1615229390468276</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cerner Corporation</t>
+          <t>Clinical Practice Research Datalink</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>145</v>
+        <v>272</v>
       </c>
       <c r="C3" t="n">
-        <v>159</v>
+        <v>360</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9119496855345912</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08163088267187169</v>
+        <v>0.215298202614379</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clinical Practice Research Datalink</t>
+          <t>Flatiron Health</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>240</v>
+        <v>552</v>
       </c>
       <c r="C4" t="n">
-        <v>327</v>
+        <v>738</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7339449541284404</v>
+        <v>0.7479674796747967</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2318425076452599</v>
+        <v>0.2121921762695889</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Flatiron Health</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>539</v>
+        <v>117</v>
       </c>
       <c r="C5" t="n">
-        <v>720</v>
+        <v>124</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7486111111111111</v>
+        <v>0.9435483870967742</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2103432282003712</v>
+        <v>0.0530741659773919</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>0.926829268292683</v>
+        <v>0.9027777777777778</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06739409499358162</v>
+        <v>0.09102564102564115</v>
       </c>
     </row>
     <row r="7">
@@ -628,187 +632,111 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04329004329004338</v>
+        <v>0.1958823529411764</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>New York University Langone Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>688</v>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>878</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.7835990888382688</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.1861657042962337</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAIL Databank</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>680</v>
+        <v>315</v>
       </c>
       <c r="C10" t="n">
-        <v>870</v>
+        <v>450</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7816091954022989</v>
+        <v>0.7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1875185936443542</v>
+        <v>0.2717460317460318</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SAIL Databank</t>
+          <t>South London and Maudsley NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>315</v>
+        <v>105</v>
       </c>
       <c r="C11" t="n">
-        <v>450</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7</v>
+        <v>0.5932203389830508</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2717460317460318</v>
+        <v>0.3452246435297284</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>South London and Maudsley NHS Foundation Trust</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>85</v>
+      </c>
+      <c r="C12" t="n">
         <v>105</v>
       </c>
-      <c r="C12" t="n">
-        <v>177</v>
-      </c>
       <c r="D12" t="n">
-        <v>0.5932203389830508</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3452246435297284</v>
+        <v>0.1570868347338936</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>The Health Improvement Network</t>
+          <t>Vanderbilt University Medical Center</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42</v>
+        <v>279</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>422</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0.6611374407582938</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TriNetX</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>85</v>
-      </c>
-      <c r="C14" t="n">
-        <v>105</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.8095238095238095</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.1570868347338936</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>University of Minnesota</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>19</v>
-      </c>
-      <c r="C15" t="n">
-        <v>28</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.6785714285714286</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.2669172932330828</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Vanderbilt University Medical Center</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>277</v>
-      </c>
-      <c r="C16" t="n">
-        <v>412</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.6723300970873787</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.2744383302372857</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Western Australian Data Linkage System</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>29</v>
-      </c>
-      <c r="C17" t="n">
-        <v>31</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.9354838709677419</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.06006674082313679</v>
+        <v>0.2835618067234029</v>
       </c>
     </row>
   </sheetData>
